--- a/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
+++ b/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="13880" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="中国银行排款明细" sheetId="1" state="visible" r:id="rId1"/>
@@ -1129,11 +1129,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
-    <col width="7.04807692307692" customWidth="1" style="9" min="4" max="4"/>
+    <col width="10.3076923076923" customWidth="1" style="9" min="4" max="4"/>
     <col width="13.2307692307692" customWidth="1" style="9" min="7" max="7"/>
     <col width="22.6153846153846" customWidth="1" style="9" min="8" max="8"/>
     <col width="24.6730769230769" customWidth="1" style="9" min="9" max="9"/>
@@ -1311,7 +1311,7 @@
         <v>189000</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>129000</v>
+        <v>144000</v>
       </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
@@ -1654,16 +1654,16 @@
       </c>
       <c r="E16" s="15" t="n"/>
       <c r="F16" s="15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>1487863</v>
+        <v>442330.75</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>680569.4</v>
+        <v>292530.75</v>
       </c>
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
@@ -1686,38 +1686,98 @@
       </c>
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="15" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>9593323.869999999</v>
+        <v>1487863</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>2131070.419999999</v>
+        <v>680569.4</v>
       </c>
       <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
       <c r="L17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="0" t="inlineStr">
+      <c r="A18" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>彭</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>9593323.869999999</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>2131070.419999999</v>
+      </c>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="C18" s="0" t="n"/>
-      <c r="D18" s="0" t="n"/>
-      <c r="E18" s="0" t="n"/>
-      <c r="F18" s="0" t="n"/>
-      <c r="G18" s="0" t="inlineStr">
+      <c r="C21" s="0" t="n"/>
+      <c r="D21" s="0" t="n"/>
+      <c r="E21" s="0" t="n"/>
+      <c r="F21" s="0" t="n"/>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="H18" s="0" t="n"/>
-      <c r="I18" s="0" t="inlineStr">
+      <c r="H21" s="0" t="n"/>
+      <c r="I21" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -1729,8 +1789,6 @@
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" priority="47" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="35" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="46" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="0.432638888888889" bottom="0.275" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" scale="32"/>
@@ -1747,7 +1805,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
-    <col width="7.04807692307692" customWidth="1" style="9" min="4" max="4"/>
+    <col width="10.3076923076923" customWidth="1" style="9" min="4" max="4"/>
     <col width="13.2307692307692" customWidth="1" style="9" min="7" max="7"/>
     <col width="22.6153846153846" customWidth="1" style="9" min="8" max="8"/>
     <col width="24.6730769230769" customWidth="1" style="9" min="9" max="9"/>
@@ -1859,8 +1917,6 @@
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1872,11 +1928,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
-    <col width="7.04807692307692" customWidth="1" style="9" min="4" max="4"/>
+    <col width="10.3076923076923" customWidth="1" style="9" min="4" max="4"/>
     <col width="13.2307692307692" customWidth="1" style="9" min="7" max="7"/>
     <col width="22.6153846153846" customWidth="1" style="9" min="8" max="8"/>
     <col width="24.6730769230769" customWidth="1" style="9" min="9" max="9"/>
@@ -2054,7 +2110,7 @@
         <v>1097167.46</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>467695.46</v>
+        <v>883975.46</v>
       </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
@@ -2278,7 +2334,7 @@
         <v>48136.65</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>23807.85</v>
+        <v>35972.25</v>
       </c>
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
@@ -2342,7 +2398,7 @@
         <v>153070.96</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>87343.95999999999</v>
+        <v>109252.96</v>
       </c>
       <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
@@ -2406,7 +2462,7 @@
         <v>66100</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>20800</v>
+        <v>43500</v>
       </c>
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
@@ -2438,7 +2494,7 @@
         <v>793439.29</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>564.290000000037</v>
+        <v>662439.29</v>
       </c>
       <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
@@ -2477,17 +2533,31 @@
       <c r="L18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="0" t="inlineStr">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G19" s="0" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I19" s="0" t="inlineStr">
+      <c r="I20" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -2499,8 +2569,6 @@
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2516,7 +2584,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
-    <col width="7.04807692307692" customWidth="1" style="9" min="4" max="4"/>
+    <col width="10.3076923076923" customWidth="1" style="9" min="4" max="4"/>
+    <col width="12.7692307692308" customWidth="1" style="9" min="5" max="5"/>
     <col width="13.2307692307692" customWidth="1" style="9" min="7" max="7"/>
     <col width="22.6153846153846" customWidth="1" style="9" min="8" max="8"/>
     <col width="24.6730769230769" customWidth="1" style="9" min="9" max="9"/>
@@ -2628,8 +2697,6 @@
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2730,7 +2797,8 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
-    <col width="7.04807692307692" customWidth="1" style="9" min="4" max="4"/>
+    <col width="10.3076923076923" customWidth="1" style="9" min="4" max="4"/>
+    <col width="12.7692307692308" customWidth="1" style="9" min="5" max="5"/>
     <col width="13.2307692307692" customWidth="1" style="9" min="7" max="7"/>
     <col width="22.6153846153846" customWidth="1" style="9" min="8" max="8"/>
     <col width="24.6730769230769" customWidth="1" style="9" min="9" max="9"/>
@@ -2844,7 +2912,7 @@
         <v>15300</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>7200</v>
+        <v>13500</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
@@ -2905,8 +2973,6 @@
   </mergeCells>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" priority="3" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="1" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
+++ b/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -1238,16 +1238,16 @@
       </c>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="15" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>1809603.14</v>
+        <v>49047</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>858213.14</v>
+        <v>39237.6</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
@@ -1273,13 +1273,13 @@
         <v>30</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>49047</v>
+        <v>189000</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>34197</v>
+        <v>151200</v>
       </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
@@ -1305,13 +1305,13 @@
         <v>30</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>189000</v>
+        <v>297620</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>144000</v>
+        <v>238096</v>
       </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
@@ -1334,16 +1334,16 @@
       </c>
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>2193548.85</v>
+        <v>378559</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>1430588.85</v>
+        <v>302847.2</v>
       </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
@@ -1366,16 +1366,16 @@
       </c>
       <c r="E7" s="15" t="n"/>
       <c r="F7" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>297620</v>
+        <v>325093.13</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>197960</v>
+        <v>260074.504</v>
       </c>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
@@ -1398,16 +1398,16 @@
       </c>
       <c r="E8" s="15" t="n"/>
       <c r="F8" s="15" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>325093.13</v>
+        <v>349192.37</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>220153.13</v>
+        <v>244434.659</v>
       </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -1430,16 +1430,16 @@
       </c>
       <c r="E9" s="15" t="n"/>
       <c r="F9" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>349192.37</v>
+        <v>113632.71</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>170552.37</v>
+        <v>90906.16800000001</v>
       </c>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
@@ -1457,21 +1457,21 @@
       <c r="C10" s="15" t="n"/>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>曹</t>
+          <t>彭</t>
         </is>
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>113632.71</v>
+        <v>471106.06</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>58732.71</v>
+        <v>277477.99</v>
       </c>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
@@ -1489,21 +1489,21 @@
       <c r="C11" s="15" t="n"/>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>曹</t>
+          <t>彭</t>
         </is>
       </c>
       <c r="E11" s="15" t="n"/>
       <c r="F11" s="15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>74100</v>
+        <v>391255.95</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>36100</v>
+        <v>271829</v>
       </c>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -1521,21 +1521,21 @@
       <c r="C12" s="15" t="n"/>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>曹</t>
+          <t>彭</t>
         </is>
       </c>
       <c r="E12" s="15" t="n"/>
       <c r="F12" s="15" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>500155.5</v>
+        <v>18800</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>112860.5</v>
+        <v>13160</v>
       </c>
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
@@ -1553,21 +1553,21 @@
       <c r="C13" s="15" t="n"/>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>曹</t>
+          <t>彭</t>
         </is>
       </c>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>11806417.61</v>
+        <v>442330.75</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>2604892.609999999</v>
+        <v>309631.525</v>
       </c>
       <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
@@ -1596,10 +1596,10 @@
         <v>60</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>471106.06</v>
+        <v>41400</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>277477.99</v>
+        <v>28980</v>
       </c>
       <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
@@ -1622,16 +1622,16 @@
       </c>
       <c r="E15" s="15" t="n"/>
       <c r="F15" s="15" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>391255.95</v>
+        <v>1487863</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>271829</v>
+        <v>1041504.1</v>
       </c>
       <c r="J15" s="15" t="n"/>
       <c r="K15" s="15" t="n"/>
@@ -1654,130 +1654,38 @@
       </c>
       <c r="E16" s="15" t="n"/>
       <c r="F16" s="15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>442330.75</v>
+        <v>9593323.869999999</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>292530.75</v>
+        <v>6715326.709</v>
       </c>
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
       <c r="L16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>彭</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>1487863</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>680569.4</v>
-      </c>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>彭</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>9593323.869999999</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>2131070.419999999</v>
-      </c>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="C21" s="0" t="n"/>
-      <c r="D21" s="0" t="n"/>
-      <c r="E21" s="0" t="n"/>
-      <c r="F21" s="0" t="n"/>
-      <c r="G21" s="0" t="inlineStr">
+      <c r="C17" s="0" t="n"/>
+      <c r="D17" s="0" t="n"/>
+      <c r="E17" s="0" t="n"/>
+      <c r="F17" s="0" t="n"/>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="H21" s="0" t="n"/>
-      <c r="I21" s="0" t="inlineStr">
+      <c r="H17" s="0" t="n"/>
+      <c r="I17" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -1801,7 +1709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -1893,19 +1801,274 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>安庆诚泰新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>544496</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>435596.8</v>
+      </c>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="n"/>
+      <c r="L3" s="15" t="n"/>
+    </row>
     <row r="4" s="9">
-      <c r="B4" s="0" t="inlineStr">
+      <c r="A4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>安庆诚泰新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="n"/>
+      <c r="L4" s="15" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>安庆诚泰新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>671732.51</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>537386.0079999999</v>
+      </c>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>安庆诚泰新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>391315.42</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>313052.336</v>
+      </c>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>广州从化兆舜新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>2878852.29</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>2303081.832</v>
+      </c>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>广州从化兆舜新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>645762.23</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>516609.784</v>
+      </c>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>广州从化兆舜新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>48136.65</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>38509.32</v>
+      </c>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>广州从化兆舜新材料有限公司</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>彭</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>66100</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>46270</v>
+      </c>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G4" s="0" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I4" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -1928,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -2037,16 +2200,16 @@
       </c>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>544496</v>
+        <v>1097167.46</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>244496</v>
+        <v>883975.46</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
@@ -2058,7 +2221,7 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>安庆诚泰新材料有限公司</t>
+          <t>广州从化兆舜新材料有限公司</t>
         </is>
       </c>
       <c r="C4" s="15" t="n"/>
@@ -2069,16 +2232,16 @@
       </c>
       <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>186535</v>
+        <v>92805.03</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>56635</v>
+        <v>74244.024</v>
       </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
@@ -2090,7 +2253,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>安庆诚泰新材料有限公司</t>
+          <t>广州从化兆舜新材料有限公司</t>
         </is>
       </c>
       <c r="C5" s="15" t="n"/>
@@ -2101,16 +2264,16 @@
       </c>
       <c r="E5" s="15" t="n"/>
       <c r="F5" s="15" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>1097167.46</v>
+        <v>3550729.78</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>883975.46</v>
+        <v>2485510.846</v>
       </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
@@ -2122,7 +2285,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>安庆诚泰新材料有限公司</t>
+          <t>广州从化兆舜新材料有限公司</t>
         </is>
       </c>
       <c r="C6" s="15" t="n"/>
@@ -2133,16 +2296,16 @@
       </c>
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>391315.42</v>
+        <v>32760</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>191315.42</v>
+        <v>26208</v>
       </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
@@ -2165,16 +2328,16 @@
       </c>
       <c r="E7" s="15" t="n"/>
       <c r="F7" s="15" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>2878852.29</v>
+        <v>230023.47</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>1723380.29</v>
+        <v>184018.776</v>
       </c>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
@@ -2197,16 +2360,16 @@
       </c>
       <c r="E8" s="15" t="n"/>
       <c r="F8" s="15" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>92805.03</v>
+        <v>302695.93</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>46005.03</v>
+        <v>242156.744</v>
       </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -2229,16 +2392,16 @@
       </c>
       <c r="E9" s="15" t="n"/>
       <c r="F9" s="15" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>3550729.78</v>
+        <v>12873.6</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>1140615.78</v>
+        <v>10298.88</v>
       </c>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
@@ -2261,16 +2424,16 @@
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" s="15" t="n">
         <v>120</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>150</v>
-      </c>
       <c r="H10" s="15" t="n">
-        <v>645762.23</v>
+        <v>153070.96</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>296313.23</v>
+        <v>122456.768</v>
       </c>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
@@ -2282,7 +2445,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>广州从化兆舜新材料有限公司</t>
+          <t>广州集泰化工股份有限公司</t>
         </is>
       </c>
       <c r="C11" s="15" t="n"/>
@@ -2293,16 +2456,16 @@
       </c>
       <c r="E11" s="15" t="n"/>
       <c r="F11" s="15" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>120</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>230023.47</v>
+        <v>11638944.6</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>105473.47</v>
+        <v>9311155.68</v>
       </c>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -2314,7 +2477,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>广州从化兆舜新材料有限公司</t>
+          <t>广州集泰化工股份有限公司</t>
         </is>
       </c>
       <c r="C12" s="15" t="n"/>
@@ -2325,16 +2488,16 @@
       </c>
       <c r="E12" s="15" t="n"/>
       <c r="F12" s="15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>48136.65</v>
+        <v>500155.5</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>35972.25</v>
+        <v>400124.4</v>
       </c>
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
@@ -2352,7 +2515,7 @@
       <c r="C13" s="15" t="n"/>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>曹</t>
+          <t>彭</t>
         </is>
       </c>
       <c r="E13" s="15" t="n"/>
@@ -2360,13 +2523,13 @@
         <v>30</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>302695.93</v>
+        <v>793439.29</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>159345.93</v>
+        <v>555407.503</v>
       </c>
       <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
@@ -2389,175 +2552,33 @@
       </c>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>153070.96</v>
+        <v>537171.05</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>109252.96</v>
+        <v>401171.05</v>
       </c>
       <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
       <c r="L14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>曹</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>11638944.6</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>6780714.6</v>
-      </c>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>广州从化兆舜新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>彭</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>66100</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>43500</v>
-      </c>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>广州从化兆舜新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>彭</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>793439.29</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>662439.29</v>
-      </c>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>广州从化兆舜新材料有限公司</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>曹</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H18" s="15" t="n">
-        <v>537171.05</v>
-      </c>
-      <c r="I18" s="15" t="n">
-        <v>401171.05</v>
-      </c>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -2912,7 +2933,7 @@
         <v>15300</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>13500</v>
+        <v>10710</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>

--- a/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
+++ b/AutoPaymentScheduleFile/DetailTemplate/给财务的贷款安排明细.xlsx
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -1222,316 +1222,246 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="15" t="n"/>
+      <c r="A3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>曹星</t>
+        </is>
+      </c>
       <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n"/>
+      <c r="F3" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>596986</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>459986</v>
+      </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
     </row>
     <row r="4" s="9">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="15" t="n"/>
+      <c r="A4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
+      <c r="F4" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>41302.25</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>8877.25</v>
+      </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>189150</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>72000</v>
+      </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>215677.11</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>215677.11</v>
+      </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
+      <c r="F7" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>50532.98</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>28273.79</v>
+      </c>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>曹星</t>
+        </is>
+      </c>
       <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
+      <c r="F8" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>119657</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>82457</v>
+      </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>曹星</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
+      <c r="F9" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>127637.5</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>127637.5</v>
+      </c>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="15" t="n"/>
-      <c r="L10" s="15" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="15" t="n"/>
-      <c r="L11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="15" t="n"/>
-      <c r="L12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="15" t="n"/>
-      <c r="L13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="15" t="n"/>
-      <c r="L20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="15" t="n"/>
-      <c r="L21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="15" t="n"/>
-      <c r="L22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="15" t="n"/>
-      <c r="K23" s="15" t="n"/>
-      <c r="L23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="C24" s="0" t="n"/>
-      <c r="D24" s="0" t="n"/>
-      <c r="E24" s="0" t="n"/>
-      <c r="F24" s="0" t="n"/>
-      <c r="G24" s="0" t="inlineStr">
+      <c r="C10" s="0" t="n"/>
+      <c r="D10" s="0" t="n"/>
+      <c r="E10" s="0" t="n"/>
+      <c r="F10" s="0" t="n"/>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="H24" s="0" t="n"/>
-      <c r="I24" s="0" t="inlineStr">
+      <c r="H10" s="0" t="n"/>
+      <c r="I10" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -1555,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -1659,21 +1589,21 @@
       <c r="C3" s="15" t="n"/>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>曹星</t>
+          <t>彭时莎</t>
         </is>
       </c>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="15" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>90</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>596986</v>
+        <v>228431.26</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>229993</v>
+        <v>33399.26</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
@@ -1691,21 +1621,21 @@
       <c r="C4" s="15" t="n"/>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>曹星</t>
+          <t>彭时莎</t>
         </is>
       </c>
       <c r="E4" s="15" t="n"/>
       <c r="F4" s="15" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>609561.75</v>
+        <v>2327185</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>192220.875</v>
+        <v>1570135</v>
       </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
@@ -1728,16 +1658,16 @@
       </c>
       <c r="E5" s="15" t="n"/>
       <c r="F5" s="15" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>228431.26</v>
+        <v>6708422</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>3339.926</v>
+        <v>6708422</v>
       </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
@@ -1760,16 +1690,16 @@
       </c>
       <c r="E6" s="15" t="n"/>
       <c r="F6" s="15" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>41302.25</v>
+        <v>29197.5</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>4438.625</v>
+        <v>29197.5</v>
       </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
@@ -1798,10 +1728,10 @@
         <v>60</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>2327185</v>
+        <v>476699.64</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>157013.5</v>
+        <v>362099.64</v>
       </c>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
@@ -1824,16 +1754,16 @@
       </c>
       <c r="E8" s="15" t="n"/>
       <c r="F8" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>12908794.6</v>
+        <v>307393</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>742531.96</v>
+        <v>222033</v>
       </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
@@ -1856,16 +1786,16 @@
       </c>
       <c r="E9" s="15" t="n"/>
       <c r="F9" s="15" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>532838.6</v>
+        <v>300160</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>202669.3</v>
+        <v>300160</v>
       </c>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
@@ -1888,16 +1818,16 @@
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>6708422</v>
+        <v>2378040</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>6708422</v>
+        <v>480840</v>
       </c>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
@@ -1920,16 +1850,16 @@
       </c>
       <c r="E11" s="15" t="n"/>
       <c r="F11" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>90</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>199320</v>
+        <v>125113.09</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>99660</v>
+        <v>84853.09</v>
       </c>
       <c r="J11" s="15" t="n"/>
       <c r="K11" s="15" t="n"/>
@@ -1952,16 +1882,16 @@
       </c>
       <c r="E12" s="15" t="n"/>
       <c r="F12" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>1793548.85</v>
+        <v>251500</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>145558.885</v>
+        <v>251500</v>
       </c>
       <c r="J12" s="15" t="n"/>
       <c r="K12" s="15" t="n"/>
@@ -1984,16 +1914,16 @@
       </c>
       <c r="E13" s="15" t="n"/>
       <c r="F13" s="15" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>2673193.33</v>
+        <v>3518271.84</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>140032.483</v>
+        <v>1005971.84</v>
       </c>
       <c r="J13" s="15" t="n"/>
       <c r="K13" s="15" t="n"/>
@@ -2016,16 +1946,16 @@
       </c>
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>29197.5</v>
+        <v>293396.19</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>29197.5</v>
+        <v>125396.19</v>
       </c>
       <c r="J14" s="15" t="n"/>
       <c r="K14" s="15" t="n"/>
@@ -2054,10 +1984,10 @@
         <v>60</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>476699.64</v>
+        <v>1160148.96</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>36209.96400000001</v>
+        <v>729148.96</v>
       </c>
       <c r="J15" s="15" t="n"/>
       <c r="K15" s="15" t="n"/>
@@ -2080,16 +2010,16 @@
       </c>
       <c r="E16" s="15" t="n"/>
       <c r="F16" s="15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>993438.6</v>
+        <v>517877.79</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>224559.3</v>
+        <v>517877.79</v>
       </c>
       <c r="J16" s="15" t="n"/>
       <c r="K16" s="15" t="n"/>
@@ -2112,16 +2042,16 @@
       </c>
       <c r="E17" s="15" t="n"/>
       <c r="F17" s="15" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>307393</v>
+        <v>67416</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>22203.3</v>
+        <v>16764</v>
       </c>
       <c r="J17" s="15" t="n"/>
       <c r="K17" s="15" t="n"/>
@@ -2144,16 +2074,16 @@
       </c>
       <c r="E18" s="15" t="n"/>
       <c r="F18" s="15" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>300160</v>
+        <v>511139.19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>300160</v>
+        <v>132384.19</v>
       </c>
       <c r="J18" s="15" t="n"/>
       <c r="K18" s="15" t="n"/>
@@ -2179,13 +2109,13 @@
         <v>60</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>2378040</v>
+        <v>600720</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>480840</v>
+        <v>293720</v>
       </c>
       <c r="J19" s="15" t="n"/>
       <c r="K19" s="15" t="n"/>
@@ -2211,13 +2141,13 @@
         <v>90</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>125113.09</v>
+        <v>33460</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>84853.09</v>
+        <v>24095</v>
       </c>
       <c r="J20" s="15" t="n"/>
       <c r="K20" s="15" t="n"/>
@@ -2235,21 +2165,21 @@
       <c r="C21" s="15" t="n"/>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>彭时莎</t>
+          <t>曹星</t>
         </is>
       </c>
       <c r="E21" s="15" t="n"/>
       <c r="F21" s="15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>251500</v>
+        <v>1050</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>25150</v>
+        <v>630</v>
       </c>
       <c r="J21" s="15" t="n"/>
       <c r="K21" s="15" t="n"/>
@@ -2267,7 +2197,7 @@
       <c r="C22" s="15" t="n"/>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>彭时莎</t>
+          <t>曹星</t>
         </is>
       </c>
       <c r="E22" s="15" t="n"/>
@@ -2275,13 +2205,13 @@
         <v>30</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>189150</v>
+        <v>2800</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>36000</v>
+        <v>2800</v>
       </c>
       <c r="J22" s="15" t="n"/>
       <c r="K22" s="15" t="n"/>
@@ -2299,1062 +2229,38 @@
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>彭时莎</t>
+          <t>曹星</t>
         </is>
       </c>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="15" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>3518271.84</v>
+        <v>75600</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>100597.184</v>
+        <v>37440</v>
       </c>
       <c r="J23" s="15" t="n"/>
       <c r="K23" s="15" t="n"/>
       <c r="L23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>293396.19</v>
-      </c>
-      <c r="I24" s="15" t="n">
-        <v>12539.619</v>
-      </c>
-      <c r="J24" s="15" t="n"/>
-      <c r="K24" s="15" t="n"/>
-      <c r="L24" s="15" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>1160148.96</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>72914.89599999999</v>
-      </c>
-      <c r="J25" s="15" t="n"/>
-      <c r="K25" s="15" t="n"/>
-      <c r="L25" s="15" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>517877.79</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>517877.79</v>
-      </c>
-      <c r="J26" s="15" t="n"/>
-      <c r="K26" s="15" t="n"/>
-      <c r="L26" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>1045260</v>
-      </c>
-      <c r="I27" s="15" t="n">
-        <v>53560</v>
-      </c>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>257725</v>
-      </c>
-      <c r="I28" s="15" t="n">
-        <v>89925</v>
-      </c>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="n"/>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G29" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>143850</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>59925</v>
-      </c>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>50532.98</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>14136.895</v>
-      </c>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>67416</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>8382</v>
-      </c>
-      <c r="J31" s="15" t="n"/>
-      <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="n"/>
-      <c r="F32" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G32" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>289256</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>104584</v>
-      </c>
-      <c r="J32" s="15" t="n"/>
-      <c r="K32" s="15" t="n"/>
-      <c r="L32" s="15" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>502453.04</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>30229.304</v>
-      </c>
-      <c r="J33" s="15" t="n"/>
-      <c r="K33" s="15" t="n"/>
-      <c r="L33" s="15" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="n"/>
-      <c r="F34" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>718459.67</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>111089.835</v>
-      </c>
-      <c r="J34" s="15" t="n"/>
-      <c r="K34" s="15" t="n"/>
-      <c r="L34" s="15" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="n"/>
-      <c r="F35" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G35" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>65400</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>16350</v>
-      </c>
-      <c r="J35" s="15" t="n"/>
-      <c r="K35" s="15" t="n"/>
-      <c r="L35" s="15" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>511139.19</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>13238.419</v>
-      </c>
-      <c r="J36" s="15" t="n"/>
-      <c r="K36" s="15" t="n"/>
-      <c r="L36" s="15" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="n"/>
-      <c r="F37" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>77220</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>38400</v>
-      </c>
-      <c r="J37" s="15" t="n"/>
-      <c r="K37" s="15" t="n"/>
-      <c r="L37" s="15" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="n"/>
-      <c r="F38" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>600720</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>293720</v>
-      </c>
-      <c r="J38" s="15" t="n"/>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="15" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="n"/>
-      <c r="F39" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>761583.73</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>98890.86500000001</v>
-      </c>
-      <c r="J39" s="15" t="n"/>
-      <c r="K39" s="15" t="n"/>
-      <c r="L39" s="15" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>319147.9</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>62566.45</v>
-      </c>
-      <c r="J40" s="15" t="n"/>
-      <c r="K40" s="15" t="n"/>
-      <c r="L40" s="15" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>33460</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>2409.5</v>
-      </c>
-      <c r="J41" s="15" t="n"/>
-      <c r="K41" s="15" t="n"/>
-      <c r="L41" s="15" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="n"/>
-      <c r="F42" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <v>210</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>263578.59</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>58769.295</v>
-      </c>
-      <c r="J42" s="15" t="n"/>
-      <c r="K42" s="15" t="n"/>
-      <c r="L42" s="15" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="G43" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>55750</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>21575</v>
-      </c>
-      <c r="J43" s="15" t="n"/>
-      <c r="K43" s="15" t="n"/>
-      <c r="L43" s="15" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="n"/>
-      <c r="F44" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>49410</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>24705</v>
-      </c>
-      <c r="J44" s="15" t="n"/>
-      <c r="K44" s="15" t="n"/>
-      <c r="L44" s="15" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C45" s="15" t="n"/>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="n"/>
-      <c r="F45" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>249093.13</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>16164.313</v>
-      </c>
-      <c r="J45" s="15" t="n"/>
-      <c r="K45" s="15" t="n"/>
-      <c r="L45" s="15" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="n"/>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>彭时莎</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="n"/>
-      <c r="F46" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>1379493.55</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>86446.655</v>
-      </c>
-      <c r="J46" s="15" t="n"/>
-      <c r="K46" s="15" t="n"/>
-      <c r="L46" s="15" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>315</v>
-      </c>
-      <c r="J47" s="15" t="n"/>
-      <c r="K47" s="15" t="n"/>
-      <c r="L47" s="15" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="n"/>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="n"/>
-      <c r="F48" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="G48" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>93100</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>27550</v>
-      </c>
-      <c r="J48" s="15" t="n"/>
-      <c r="K48" s="15" t="n"/>
-      <c r="L48" s="15" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>2382359.5</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>593364.425</v>
-      </c>
-      <c r="J49" s="15" t="n"/>
-      <c r="K49" s="15" t="n"/>
-      <c r="L49" s="15" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="n"/>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="n"/>
-      <c r="F50" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>119657</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>41228.5</v>
-      </c>
-      <c r="J50" s="15" t="n"/>
-      <c r="K50" s="15" t="n"/>
-      <c r="L50" s="15" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="n"/>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="n"/>
-      <c r="F51" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G51" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="J51" s="15" t="n"/>
-      <c r="K51" s="15" t="n"/>
-      <c r="L51" s="15" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="n"/>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="n"/>
-      <c r="F52" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="G52" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>3791663.21</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>144154.663</v>
-      </c>
-      <c r="J52" s="15" t="n"/>
-      <c r="K52" s="15" t="n"/>
-      <c r="L52" s="15" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="n"/>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="n"/>
-      <c r="F53" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G53" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>75600</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>3744</v>
-      </c>
-      <c r="J53" s="15" t="n"/>
-      <c r="K53" s="15" t="n"/>
-      <c r="L53" s="15" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="n"/>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G54" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>127637.5</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>63818.75</v>
-      </c>
-      <c r="J54" s="15" t="n"/>
-      <c r="K54" s="15" t="n"/>
-      <c r="L54" s="15" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="n"/>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="n"/>
-      <c r="F55" s="15" t="n">
-        <v>120</v>
-      </c>
-      <c r="G55" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>12262292.61</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>272449.2609999999</v>
-      </c>
-      <c r="J55" s="15" t="n"/>
-      <c r="K55" s="15" t="n"/>
-      <c r="L55" s="15" t="n"/>
-    </row>
-    <row r="56">
-      <c r="B56" s="0" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G56" s="0" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I56" s="0" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -3503,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -3608,70 +2514,38 @@
       <c r="C3" s="15" t="n"/>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>彭时莎</t>
+          <t>曹星</t>
         </is>
       </c>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="15" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>180</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>2509963.83</v>
+        <v>2088276.03</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>1042081.915</v>
+        <v>296411.03</v>
       </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
     </row>
     <row r="4" s="9">
-      <c r="A4" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>广州集泰化工股份有限公司</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>曹星</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>2088276.03</v>
-      </c>
-      <c r="I4" s="15" t="n">
-        <v>29641.103</v>
-      </c>
-      <c r="J4" s="15" t="n"/>
-      <c r="K4" s="15" t="n"/>
-      <c r="L4" s="15" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
@@ -3779,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
     <col width="13.1442307692308" customWidth="1" style="9" min="3" max="3"/>
@@ -3873,255 +2747,273 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="15" t="n"/>
+      <c r="A3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="15" t="n"/>
+      <c r="F3" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>532838.6</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>405338.6</v>
+      </c>
       <c r="J3" s="15" t="n"/>
       <c r="K3" s="15" t="n"/>
       <c r="L3" s="15" t="n"/>
     </row>
     <row r="4" s="9">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="15" t="n"/>
+      <c r="A4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="15" t="n"/>
-      <c r="I4" s="15" t="n"/>
+      <c r="F4" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>993438.6</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>449118.6</v>
+      </c>
       <c r="J4" s="15" t="n"/>
       <c r="K4" s="15" t="n"/>
       <c r="L4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
+      <c r="A5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E5" s="15" t="n"/>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
+      <c r="F5" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>544076.1899999999</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>425576.19</v>
+      </c>
       <c r="J5" s="15" t="n"/>
       <c r="K5" s="15" t="n"/>
       <c r="L5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="15" t="n"/>
+      <c r="A6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>15250</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>15250</v>
+      </c>
       <c r="J6" s="15" t="n"/>
       <c r="K6" s="15" t="n"/>
       <c r="L6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
+      <c r="F7" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>257725</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>179850</v>
+      </c>
       <c r="J7" s="15" t="n"/>
       <c r="K7" s="15" t="n"/>
       <c r="L7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
+      <c r="A8" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E8" s="15" t="n"/>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
+      <c r="F8" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>143850</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>119850</v>
+      </c>
       <c r="J8" s="15" t="n"/>
       <c r="K8" s="15" t="n"/>
       <c r="L8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>彭时莎</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
+      <c r="F9" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>298657.5</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>210412.5</v>
+      </c>
       <c r="J9" s="15" t="n"/>
       <c r="K9" s="15" t="n"/>
       <c r="L9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
+      <c r="A10" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>广州集泰化工股份有限公司</t>
+        </is>
+      </c>
       <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>曹星</t>
+        </is>
+      </c>
       <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>2382359.5</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>1186728.85</v>
+      </c>
       <c r="J10" s="15" t="n"/>
       <c r="K10" s="15" t="n"/>
       <c r="L10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="15" t="n"/>
-      <c r="L11" s="15" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="15" t="n"/>
-      <c r="L12" s="15" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="15" t="n"/>
-      <c r="L13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="15" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="15" t="n"/>
-      <c r="L16" s="15" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="15" t="n"/>
-      <c r="L17" s="15" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="15" t="n"/>
-      <c r="L18" s="15" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="15" t="n"/>
-      <c r="L19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>编制</t>
         </is>
       </c>
-      <c r="G20" s="0" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>采购总经理审核</t>
         </is>
       </c>
-      <c r="I20" s="0" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>财务总经理审批</t>
         </is>
